--- a/Result/profitability/3231.xlsx
+++ b/Result/profitability/3231.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.21</v>
       </c>
       <c r="M2" t="n">
-        <v>2.0875</v>
+        <v>2.49375</v>
       </c>
       <c r="N2" t="n">
-        <v>6.6175</v>
+        <v>6.28125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.03</v>
       </c>
       <c r="M3" t="n">
-        <v>2.0325</v>
+        <v>2.39</v>
       </c>
       <c r="N3" t="n">
-        <v>6.3575</v>
+        <v>6.05375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>1.98375</v>
+        <v>2.3425</v>
       </c>
       <c r="N4" t="n">
-        <v>6.04875</v>
+        <v>5.78</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.04</v>
       </c>
       <c r="M5" t="n">
-        <v>1.8825</v>
+        <v>2.1975</v>
       </c>
       <c r="N5" t="n">
-        <v>5.68</v>
+        <v>5.8325</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>1.725</v>
+        <v>2.02</v>
       </c>
       <c r="N6" t="n">
-        <v>5.74375</v>
+        <v>5.5275</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.23</v>
       </c>
       <c r="M7" t="n">
-        <v>1.58375</v>
+        <v>1.8375</v>
       </c>
       <c r="N7" t="n">
-        <v>5.54375</v>
+        <v>5.54875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.59</v>
       </c>
       <c r="M8" t="n">
-        <v>1.44625</v>
+        <v>1.65375</v>
       </c>
       <c r="N8" t="n">
-        <v>5.545000000000001</v>
+        <v>5.60125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>1.3175</v>
       </c>
       <c r="N10" t="n">
-        <v>5.48125</v>
+        <v>5.481249999999999</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>895443</v>
+      </c>
+      <c r="D75" t="n">
+        <v>844779</v>
+      </c>
+      <c r="E75" t="n">
+        <v>50664</v>
+      </c>
+      <c r="F75" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="G75" t="n">
+        <v>33447</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.74%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-2363</v>
+      </c>
+      <c r="J75" t="n">
+        <v>31084</v>
+      </c>
+      <c r="K75" t="n">
+        <v>14827</v>
+      </c>
+      <c r="L75" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.52625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>6.57125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5424836601307188</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.4500000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.08637236084452971</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.145454545454545</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2747747747747746</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
